--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -837,10 +837,14 @@
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:11:23.761Z</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
           <t>.480911634477292:fd9b5fb0b1e71be58e9a29eb9f332c19_6a34ad92a75988fec5d0deab.6a34b0c2a75988fec5d0dead.6a34b0c29ad333c21ecd7986:Trae CN.T(2026/6/19 11:00:18)</t>
@@ -848,38 +852,103 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="n"/>
-      <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="2" t="n"/>
-      <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
-      <c r="AE2" s="2" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:11:23.760Z</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Trae 生成了 Vue3/Vite 前端、Express/multer 上传服务和 dist 构建产物，但没有 README、一键启动脚本或测试记录，日志也没有构建、上传链路或全屏交互验证证据。功能上主图轮播、视频上传入口和全屏查看框架基本具备，但视频上传结果只保存在 ProductMedia 内部，App.vue 未同步 productVideo；FullscreenViewer 的滚轮缩放事件绑定在 pointer-events:none 的图片上，存在交互失效风险。</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>缺少可复跑说明；缺少自动化/人工验证证据；视频上传状态未回写业务层；全屏缩放交互实现风险；上传接口校验不够贴合视频场景</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>src/App.vue
+src/components/ProductMedia.vue
+src/components/VideoPlayer.vue
+src/components/FullscreenViewer.vue
+server/server.js
+package.json
+server/package.json
+vite.config.js</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>补齐销售详情媒体区启动说明和验证，修复视频上传状态回写、全屏滚轮缩放交互，并增加上传链路自测记录</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>01-bootstrap-and-publish.sh</t>
+        </is>
+      </c>
       <c r="AF2" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="n"/>
-      <c r="AH2" s="2" t="n"/>
-      <c r="AI2" s="2" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>2572503aac2a1055f5f06eb33d6d8910e7cd333a</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/2572503aac2a1055f5f06eb33d6d8910e7cd333a</t>
+        </is>
+      </c>
       <c r="AJ2" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr"/>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T03:00:19.076Z</t>
-        </is>
-      </c>
-      <c r="AM2" s="6" t="n"/>
-      <c r="AN2" s="6" t="n"/>
-      <c r="AO2" s="6" t="n"/>
-      <c r="AP2" s="6" t="n"/>
+          <t>2026-06-19T03:11:36.782Z</t>
+        </is>
+      </c>
+      <c r="AM2" s="6" t="inlineStr">
+        <is>
+          <t>投递：本轮实际投递内容与短提示词一致，要求基于 Vue 和 Node 开发销售详情顶部媒体区，支持商品主图轮播、视频上传、全屏展示。等待：.trae-worker-logs/worker-9324-20260619-main/worker-20260619-110001.log 显示 2026-06-19 11:00:01 初始化 worker，11:00:24 到 11:09:25 多次 heartbeat，说明 Trae CN 在等待执行。审查/保留：git status 显示全部为未跟踪文件，未看到差异审查或选择性保留记录；项目内 .trae-codex-analysis 目录为空。完成：本地生成了 package.json、vite.config.js、src/components/*.vue、server/server.js、dist 等产物，TRAE 状态为 completed。验证证据：日志没有 npm run build、服务启动、接口上传、浏览器全屏查看等记录；只能看到 dist 已存在、vite.config.js 配置 /api 代理到 3001、server/package.json 提供 start/dev 脚本，无法证明 Trae 实际跑通过端到端验证。</t>
+        </is>
+      </c>
+      <c r="AN2" s="6" t="inlineStr">
+        <is>
+          <t>产出完成了基础 Vue3 商品详情页：App.vue 引入 ProductMedia，ProductMedia 组合 ImageCarousel、VideoPlayer、FullscreenViewer；ImageCarousel 支持主图轮播、缩略图、自动播放和点击全屏；VideoPlayer 支持选择/拖拽视频、XHR 上传进度、播放控制和全屏入口；server/server.js 使用 Express/multer 提供 /api/upload 和 /uploads 静态访问，vite.config.js 将 /api 代理到 http://localhost:3001。缺失点是项目没有 README 或根级并发脚本，接手者需要分别在根目录和 server 目录启动；没有测试文件或验证脚本；App.vue 的 onVideoUploaded 只 console.log，ProductMedia 也只 emit video-uploaded，没有把上传后的 URL 同步到 productVideo 或对外暴露 v-model，刷新/重建组件后状态不可依赖；FullscreenViewer.vue 第 30 行把 @wheel.prevent 绑在 img 上，但第 345 行 .viewer-image 设置 pointer-events:none，滚轮缩放很可能不会触发；server/server.js 的上传过滤允许图片和视频，而当前前端视频上传场景没有在服务端强约束视频类型。</t>
+        </is>
+      </c>
+      <c r="AO2" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae 日志只有初始化、heartbeat 和分析启动记录，没有展示执行了哪些命令，也没有留下构建、启动前后端、上传样例视频、检查全屏图片/视频展示的证据；README、环境样例和 CI 仍缺失，和本地扫描基线中的可复跑问题一致。产物问题：虽然界面和服务代码较完整，但视频上传成功后业务层状态没有真正回写，App.vue 只打印上传数据；全屏图片的滚轮缩放事件和 CSS pointer-events:none 冲突，交互可能不可用；上传服务接受图片类型，与“视频上传”功能边界不一致；缺少测试或人工验收说明，不能确认轮播、上传、全屏视频播放在本地完整跑通。</t>
+        </is>
+      </c>
+      <c r="AP2" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git status、项目文件列表、.trae-worker-logs/worker-9324-20260619-main/worker-20260619-110001.log、package.json、server/package.json、vite.config.js、src/App.vue、src/components/ProductMedia.vue、src/components/ImageCarousel.vue、src/components/VideoPlayer.vue、src/components/FullscreenViewer.vue、src/style.css、server/server.js，并确认未发现 README、.env.example、测试文件或 GitHub Actions。未修改任何文件，也未执行会写入项目目录的构建/启动命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-110938.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1239,17 +1308,25 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:11:48.406Z</t>
+        </is>
+      </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>.480911634477292:70e8f138fb55dddbc30acc31916a7634_6a34b373a75988fec5d0df38.6a34b375a75988fec5d0df3a.6a34b3759ad333c21ecd7987:Trae CN.T(2026/6/19 11:11:49)</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -1271,13 +1348,13 @@
       <c r="AI5" s="4" t="n"/>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK5" s="4" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK5" s="4" t="inlineStr"/>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T03:11:50.351Z</t>
         </is>
       </c>
       <c r="AM5" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1318,10 +1318,14 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:17:00.234Z</t>
+        </is>
+      </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
           <t>.480911634477292:70e8f138fb55dddbc30acc31916a7634_6a34b373a75988fec5d0df38.6a34b375a75988fec5d0df3a.6a34b3759ad333c21ecd7987:Trae CN.T(2026/6/19 11:11:49)</t>
@@ -1329,38 +1333,94 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:17:00.233Z</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>Trae CN 在 `src/App.vue` 接入了规格选择和底部合计，并新增 `src/components/ProductSpec.vue` 实现多规格、SKU 调价、库存和数量联动，但新增组件仍是未跟踪文件，普通 `git diff --stat` 未计入该核心产物。功能存在初始价格未主动同步父组件、SKU 匹配依赖对象顺序、0 库存组合仍可能允许数量为 1、移动端底部购买栏可能被新增合计区域挤压等风险；未发现测试文件、构建输出或日志验证证据。</t>
+        </is>
+      </c>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>新增核心文件未跟踪；功能边界未覆盖；初始状态同步风险；库存/数量逻辑风险；移动端布局风险；缺少构建和测试验证</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>src/App.vue
+src/components/ProductSpec.vue
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>补齐规格选择模块验证与边界修复：确保 ProductSpec 纳入版本变更，初始化即同步价格，按规格组顺序匹配 SKU，禁止 0 库存组合购买，并验证移动端底部栏不溢出</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr">
+        <is>
+          <t>9307643841b0f7a3fb4c4f9ffae60f74a70556da</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/9307643841b0f7a3fb4c4f9ffae60f74a70556da</t>
+        </is>
+      </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK5" s="4" t="inlineStr"/>
       <c r="AL5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T03:11:50.351Z</t>
-        </is>
-      </c>
-      <c r="AM5" s="6" t="n"/>
-      <c r="AN5" s="6" t="n"/>
-      <c r="AO5" s="6" t="n"/>
-      <c r="AP5" s="6" t="n"/>
+          <t>2026-06-19T03:17:13.346Z</t>
+        </is>
+      </c>
+      <c r="AM5" s="6" t="inlineStr">
+        <is>
+          <t>投递：本轮实际投递内容为“增加规格选择模块，支持多种规格和对应价格自动计算销售总价”，TRAE 状态为 completed，是否完成标记为是。等待：提供的 copiedSessionId 指向 Trae CN 会话，但日志尾部为“未读取到日志”，无法从日志确认其内部步骤、命令执行或自测过程。审查/保留：工作区保留了 `src/App.vue` 修改、`src/components/ProductSpec.vue` 未跟踪新增文件，以及任务跟踪表 xlsx 修改；未看到回滚迹象。完成：产物层面已经出现规格模块 UI、规格组数据、SKU 价格/库存数据、数量控件和底部合计展示。验证证据：只读检查了 `git status --short`、`git diff --stat`、`git diff -- src/App.vue`、`src/components/ProductSpec.vue` 内容、`package.json` 脚本和测试文件搜索；没有读取到 Trae 日志，没有发现测试文件，也没有运行构建，因为本次要求只读分析且构建会产生文件写入。</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="inlineStr">
+        <is>
+          <t>Trae CN 完成了主体功能搭建：`App.vue` 引入 `ProductSpec`，将商品基础价格、规格组和 SKU 列表传入组件，并通过 `price-change` 更新商品展示价和底部合计；`ProductSpec.vue` 提供已选规格展示、多规格按钮、禁用单项 0 库存选项、数量加减、单价和合计计算。缺口是核心新增组件处于未跟踪状态，若后续只提交已跟踪 diff 会直接丢失功能；组件初始化默认规格后没有立即 emit `price-change`，父组件初始展示价只等于基础价；SKU key 通过 `Object.values(selectedSpecs).join('-')` 生成，依赖对象键顺序而不是显式按 `specGroups` 顺序，扩展动态规格时有错配风险；`maxQuantity` 使用 `Math.max(1, currentStock)`，一旦 SKU 组合库存为 0 仍可能保留可购买数量 1；底部固定购买栏新增合计区域后未做响应式收缩，窄屏可能挤压按钮。项目仍无测试文件，`package.json` 只有 `dev/build/preview` 脚本，本轮未见构建或浏览器验证记录。</t>
+        </is>
+      </c>
+      <c r="AO5" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae CN 标记 completed 但没有可读取日志，无法证明是否执行过安装、构建、预览或交互验证；核心新增文件未进入 git 跟踪，说明完成状态与可交付状态不一致；任务跟踪表 xlsx 被修改但没有可审查的文本说明支撑。产物问题：规格选择功能只覆盖了常规演示路径，初始化同步、SKU 顺序匹配、0 库存组合、移动端底部栏宽度这些直接影响购买链路的边界没有处理；没有新增测试或验证说明，无法证明“多种规格和对应价格自动计算销售总价”在不同组合、数量和库存状态下稳定成立。</t>
+        </is>
+      </c>
+      <c r="AP5" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 `git status --short`、`git diff --stat`、`git diff -- src/App.vue`、`sed -n` 读取的 `src/App.vue` 与 `src/components/ProductSpec.vue`、`package.json`，并用 `rg --files -g '*test*' -g '*spec*' -g '!node_modules'` 搜索测试文件、用 `git ls-files src/components/ProductSpec.vue --error-unmatch` 确认新增组件未被 git 跟踪。未修改任何文件，未运行会写入产物的构建命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-111555.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1720,17 +1780,25 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:17:28.917Z</t>
+        </is>
+      </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W8" s="2" t="n"/>
-      <c r="X8" s="2" t="n"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>.480911634477292:981c086fafa21ff41527da3f959f9d5b_6a34b4c8a75988fec5d0dfa6.6a34b4c9a75988fec5d0dfa8.6a34b4c99ad333c21ecd7988:Trae CN.T(2026/6/19 11:17:29)</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -1752,13 +1820,13 @@
       <c r="AI8" s="2" t="n"/>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK8" s="2" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr"/>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T03:17:30.891Z</t>
         </is>
       </c>
       <c r="AM8" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1790,10 +1790,14 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:26:52.144Z</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
           <t>.480911634477292:981c086fafa21ff41527da3f959f9d5b_6a34b4c8a75988fec5d0dfa6.6a34b4c9a75988fec5d0dfa8.6a34b4c99ad333c21ecd7988:Trae CN.T(2026/6/19 11:17:29)</t>
@@ -1801,38 +1805,93 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="n"/>
-      <c r="AA8" s="2" t="n"/>
-      <c r="AB8" s="2" t="n"/>
-      <c r="AC8" s="2" t="n"/>
-      <c r="AD8" s="2" t="n"/>
-      <c r="AE8" s="2" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:26:52.143Z</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>Trae CN 只在 `src/components/ProductSpec.vue` 做了 13 行响应式触发修补，能让默认规格初始化和点击选择通过整体替换对象触发 `price-change`，但没有提供浏览器交互、构建或测试证据证明“选择销售规格后销售总价实时更新”已回归。修复没有解释真实根因，因为当前 Vue 3 deep watch 对对象属性修改本身可触发，且仍保留 SKU key 顺序依赖、0 库存数量不一致等原有风险；同时任务跟踪表 xlsx 被二进制修改，无法审查内容。</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>验证证据不足；根因定位不足；响应式修复偏表层；SKU匹配顺序风险；库存数量边界风险；二进制产物不可审查</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>src/components/ProductSpec.vue
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>补充规格选择价格实时更新的可验证修复：定位父子组件价格同步根因，保留对象整体更新或改为明确监听计算值，按 specGroups 顺序生成 SKU key，修复 0 库存数量边界，并用构建和浏览器交互验证所有规格组合的合计实时变化</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG8" s="2" t="n"/>
-      <c r="AH8" s="2" t="n"/>
-      <c r="AI8" s="2" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>bc32363a78b132fea0d23fb895798b1bdeed4618</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/bc32363a78b132fea0d23fb895798b1bdeed4618</t>
+        </is>
+      </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK8" s="2" t="inlineStr"/>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T03:17:30.891Z</t>
-        </is>
-      </c>
-      <c r="AM8" s="6" t="n"/>
-      <c r="AN8" s="6" t="n"/>
-      <c r="AO8" s="6" t="n"/>
-      <c r="AP8" s="6" t="n"/>
+          <t>2026-06-19T03:27:05.787Z</t>
+        </is>
+      </c>
+      <c r="AM8" s="6" t="inlineStr">
+        <is>
+          <t>投递：本轮短提示词和实际投递内容均为“修复选择销售规格后销售总价没有实时更新”，TRAE 状态给定为 completed，是否完成给定为是。等待：本地 `.trae-worker-logs/worker-9324-20260619-main/worker-20260619-110001.log` 显示 row8 Bug 修复-1 于 2026-06-19 11:17:45 后开始 heartbeat，并在 11:24:46 启动 Codex CLI 只读分析；日志尾部只有 heartbeat 到 11:26:06，没有看到 row8 child exited、commit、构建、预览或交互验证记录。审查/保留：当前 `git status --short` 显示 `src/components/ProductSpec.vue` 和 `YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx` 被修改；`git diff --stat` 显示组件 9 行新增、4 行删除，xlsx 为二进制大小变化。完成：代码层面 Trae 把 `initDefaultSpecs` 改成先拷贝再整体赋值，把 `selectSpec` 改成整体替换 `selectedSpecs.value`，并将 `initDefaultSpecs()` 从 watcher 之前移动到 watcher 之后。验证证据：只读检查了 git diff、HEAD 版本、当前组件、父组件价格接入、package 脚本、测试文件搜索和 worker 日志；未运行会写入 dist 的构建命令，未修改任何文件。</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="inlineStr">
+        <is>
+          <t>Trae CN 的产出完成了一个窄范围修复：`selectedSpecs` 初始化和点击选择都改为替换整个对象引用，watcher 注册后再执行默认规格初始化，因此父组件通过 `price-change` 接收初始价格和后续选择价格的概率更高；`App.vue` 已有 `@price-change="onPriceChange"`，会把 `currentUnitPrice` 和 `currentTotalPrice` 更新到顶部价格和底部合计。缺失是没有新增测试、没有浏览器点击不同颜色/版本后的截图或日志、没有 `npm run build` 证据，也没有说明为什么原来的 deep watch 失效；我用当前依赖的 Vue 最小示例验证了 `watch(ref({}), ..., { deep: true })` 对属性修改会触发，所以 Trae 的“对象整体替换”更像规避性修补而不是被证明的根因修复。风险仍在：`specPriceAdjust` 和 `currentStock` 用 `Object.values(selectedSpecs.value).join('-')` 匹配 SKU，依赖对象键顺序；0 库存 SKU 下 watcher 可能把 quantity 置为 0，而 `maxQuantity` 又强制至少 1，购买数量状态不一致；xlsx 二进制改动无法确认是否只是任务记录更新。</t>
+        </is>
+      </c>
+      <c r="AO8" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae CN 标记 completed，但可见日志没有 row8 完成摘要、没有构建命令、没有启动页面、没有模拟选择规格并观察总价变化的验证证据；任务跟踪表被修改但属于二进制文件，无法从 diff 审查其内容是否必要。产物问题：`ProductSpec.vue` 的修复只改响应式赋值方式，没有补上针对“选择规格后父组件总价实时更新”的测试或交互验证；根因解释不足，Vue 3 deep watch 本可监听原先的属性修改；SKU 顺序匹配和 0 库存数量边界仍会影响销售规格价格/库存链路，后续换数据结构或选择无库存组合时仍可能出现错误。</t>
+        </is>
+      </c>
+      <c r="AP8" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 `git status --short`、`git diff --stat`、`git diff -- src/components/ProductSpec.vue`、`git show HEAD:src/components/ProductSpec.vue`、`sed -n` 读取的 `src/components/ProductSpec.vue` 与 `src/App.vue`、`package.json`、`.trae-worker-logs/worker-9324-20260619-main/worker-20260619-110001.log`，使用 `rg` 搜索 ProductSpec/price-change/测试文件，并用只读 Node/Vue 最小示例确认 deep watch 对对象属性修改会触发。未修改任何文件，未运行会写入构建产物的命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-112501.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2184,17 +2243,25 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:27:09.201Z</t>
+        </is>
+      </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W11" s="4" t="n"/>
-      <c r="X11" s="4" t="n"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>.480911634477292:0a33372f87902721abe82c26b1aabb87_6a34b70ca75988fec5d0e030.6a34b70ea75988fec5d0e032.6a34b70d9ad333c21ecd7989:Trae CN.T(2026/6/19 11:27:10)</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -2216,13 +2283,13 @@
       <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK11" s="4" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK11" s="4" t="inlineStr"/>
       <c r="AL11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T03:27:11.187Z</t>
         </is>
       </c>
       <c r="AM11" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -2253,10 +2253,14 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:38:45.190Z</t>
+        </is>
+      </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
           <t>.480911634477292:0a33372f87902721abe82c26b1aabb87_6a34b70ca75988fec5d0e030.6a34b70ea75988fec5d0e032.6a34b70d9ad333c21ecd7989:Trae CN.T(2026/6/19 11:27:10)</t>
@@ -2264,38 +2268,100 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="4" t="n"/>
-      <c r="AE11" s="4" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:38:45.189Z</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>本轮在 server/server.js 增加了商品、销量、库存和下单 mock 接口，也新增了 src/api 与 useProductSpec 抽离逻辑，但库存接口没有真正接入前端：src/App.vue 仍硬编码 skuList，src/components/ProductSpec.vue 还把 enableServerSync 设为 false。售罄规格因 specGroups 不带 stock 仍可被选择，下单后只刷新销量不刷新库存，且 /api/order/create 缺少 productId 与 quantity 严格校验；只读检查仅确认新增 JS 语法通过，未发现测试或构建验证记录。</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>接口逻辑半接入；库存状态不同步；售罄规格可选；下单参数校验不足；缺少构建/测试验证；本轮产物未提交</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>server/server.js
+src/App.vue
+src/components/ProductSpec.vue
+src/api/index.js
+src/api/product.js
+src/api/order.js
+src/api/request.js
+src/composables/useProductSpec.js
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>打通真实 SKU 库存接口并补齐下单后库存刷新和参数校验</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
+          <t>744bc4a0a9a580d9a8fa8a3a33672947f087cf91</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/744bc4a0a9a580d9a8fa8a3a33672947f087cf91</t>
+        </is>
+      </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK11" s="4" t="inlineStr"/>
       <c r="AL11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T03:27:11.187Z</t>
-        </is>
-      </c>
-      <c r="AM11" s="6" t="n"/>
-      <c r="AN11" s="6" t="n"/>
-      <c r="AO11" s="6" t="n"/>
-      <c r="AP11" s="6" t="n"/>
+          <t>2026-06-19T03:38:58.509Z</t>
+        </is>
+      </c>
+      <c r="AM11" s="6" t="inlineStr">
+        <is>
+          <t>实际投递内容为“重构销售规格、库存、已售数量和立即购买的接口逻辑”，copiedSessionId 对应 Trae CN 2026/6/19 11:27:10。本地 .trae-worker-logs/worker-9324-20260619-main/latest.log 显示 row11 代码重构-1 于 11:27:26 启动，持续 heartbeat，到 11:36:56 进入 Codex CLI 只读分析；日志尾部未看到 row11 child exited 或提交摘要，completed 状态来自用户提供的 TRAE 状态字段。审查保留证据为 git status 中 server/server.js、src/App.vue、src/components/ProductSpec.vue、任务跟踪表修改，以及 src/api、src/composables 新增；git log 最新提交仍是上一轮 Bug 修复-1 的 bc32363，未看到本轮 copiedSessionId 的提交。验证证据：对 server/server.js、src/api/*.js、src/composables/useProductSpec.js 执行 node --check 均退出码 0；未运行 npm run build，因为只读分析且构建会写 dist；find 未发现项目测试文件，package.json 也无 test 脚本。</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="inlineStr">
+        <is>
+          <t>Trae 完成了表层重构：后端新增 mockProduct、/api/product/:id、/api/product/:id/sales、/api/product/:id/stock、/api/order/create；前端新增 request/product/order API 封装，App.vue 改为异步拉商品详情和销量，ProductSpec.vue 把选择、数量、价格计算抽到 useProductSpec。缺口在接口链路没有闭环：server 的商品详情没有返回 skuList，App.vue 的 fetchSkuList 仍在 170-185 行硬编码库存；ProductSpec.vue 115-118 行显式关闭 enableServerSync，导致 useProductSpec 124-138 行的 getSkuStock 基本闲置；下单成功后 App.vue 199-202 行只刷新销量，库存刷新只有空注释，当前 SKU 库存不会同步扣减。风险包括：specGroups options 不包含 stock，而 ProductSpec.vue 18-21 行依赖 option.stock === 0 禁用按钮，售罄的玫瑰金组合仍可选择；useProductSpec.js 96-98 行把 0 库存 maxQuantity 强行变成 1，用户界面仍显示可买 1 件；server/server.js 183-199 行未校验 productId 是否匹配、quantity 是否正整数，负数或小数请求会造成库存/销量异常；销量和库存全部是内存态，服务重启即重置。</t>
+        </is>
+      </c>
+      <c r="AO11" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae 标记 completed，但本地日志没有读到本轮完成摘要和验证命令输出，git log 也没有本轮提交；改动同时触及任务跟踪表 xlsx，但无法从代码证据判断其必要性；没有测试、没有构建记录，无法证明“销售规格、库存、已售数量、立即购买”四条链路被端到端验证。产物问题：库存接口虽然存在，但前端仍使用硬编码 skuList 且关闭服务端库存同步，下单后也不刷新库存；售罄规格禁用逻辑依赖缺失字段，导致 0 库存组合可选；立即购买没有前端空 SKU 防护之外的完整校验，后端也缺少 productId/quantity 约束；重构把逻辑拆到 composable 和 api 层，但没有消除数据重复，反而形成 server mock、App mockSkuList、ProductSpec 本地状态三套库存来源。</t>
+        </is>
+      </c>
+      <c r="AP11" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git status、git diff --stat、git diff --name-only、git diff --numstat、git log --oneline、server/server.js、src/App.vue、src/components/ProductSpec.vue、src/api/index.js、src/api/product.js、src/api/order.js、src/api/request.js、src/composables/useProductSpec.js、package.json、server/package.json、.trae-worker-logs/worker-9324-20260619-main/latest.log。尝试读取项目根 RTK.md 和上级 RTK.md 未找到；find 未发现 README、.env.example、.github/workflows 或项目测试文件；执行 node --check 验证新增 JS 语法通过，未执行会写入产物的构建命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-113656.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2379,17 +2445,25 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:39:10.152Z</t>
+        </is>
+      </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W12" s="2" t="n"/>
-      <c r="X12" s="2" t="n"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>.480911634477292:925456f396d6805851f4d5d62024e2fa_6a34b9dda75988fec5d0e0da.6a34b9dfa75988fec5d0e0dc.6a34b9de9ad333c21ecd798a:Trae CN.T(2026/6/19 11:39:11)</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -2411,13 +2485,13 @@
       <c r="AI12" s="2" t="n"/>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK12" s="2" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr"/>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T03:39:12.397Z</t>
         </is>
       </c>
       <c r="AM12" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1040,51 +1040,59 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:55:52.024Z</t>
+        </is>
+      </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
+      <c r="W3" s="4" t="inlineStr"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>.480911634477292:d808200ea68af7eb9f3630ad74289926_6a34bdc7a75988fec5d0e1ad.6a34bdc8a75988fec5d0e1af.6a34bdc89ad333c21ecd798c:Trae CN.T(2026/6/19 11:55:52)</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="inlineStr"/>
+      <c r="AE3" s="4" t="inlineStr"/>
       <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>未提交</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="n"/>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr"/>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK3" s="4" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="inlineStr"/>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
-        </is>
-      </c>
-      <c r="AM3" s="6" t="n"/>
-      <c r="AN3" s="6" t="n"/>
-      <c r="AO3" s="6" t="n"/>
-      <c r="AP3" s="6" t="n"/>
+          <t>2026-06-19T03:55:54.331Z</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="inlineStr"/>
+      <c r="AN3" s="6" t="inlineStr"/>
+      <c r="AO3" s="6" t="inlineStr"/>
+      <c r="AP3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2455,10 +2463,14 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:52:37.227Z</t>
+        </is>
+      </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
           <t>.480911634477292:925456f396d6805851f4d5d62024e2fa_6a34b9dda75988fec5d0e0da.6a34b9dfa75988fec5d0e0dc.6a34b9de9ad333c21ecd798a:Trae CN.T(2026/6/19 11:39:11)</t>
@@ -2466,38 +2478,104 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="n"/>
-      <c r="AA12" s="2" t="n"/>
-      <c r="AB12" s="2" t="n"/>
-      <c r="AC12" s="2" t="n"/>
-      <c r="AD12" s="2" t="n"/>
-      <c r="AE12" s="2" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T03:52:37.226Z</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>Trae CN 已新增 Vitest/Supertest 测试，覆盖了销售规格价格、库存扣减、销量累加和详情富文本的主要正向路径，但同时改了 server/server.js、src/App.vue、src/api/product.js 并新增 ProductDescription.vue，超出了“单元测试”范围。关键不足是规格 SKU 匹配仍依赖 selectedSpecs 对象插入顺序，测试只覆盖 color→version 顺序；库存扣减后前端 skuList 仍是硬编码且 handleBuyNow 中库存刷新为空注释；富文本用 v-html 直接渲染，测试只验证渲染成功，没有验证清洗或安全边界。未读取到 Trae 日志，当前只读环境执行 npm test 因 Vite 需要写 node_modules/.vite-temp 触发 EPERM，缺少可确认的 Trae 运行通过证据。</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>测试覆盖不足；验证证据缺失；运行时代码范围过大；前端库存同步缺口；富文本安全边界缺失；测试隔离不严</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>package.json
+package-lock.json
+vitest.config.js
+tests/useProductSpec.test.js
+tests/server.test.js
+tests/description.test.js
+server/server.js
+src/composables/useProductSpec.js
+src/components/ProductDescription.vue
+src/components/ProductSpec.vue
+src/App.vue
+src/api/product.js
+src/api/index.js</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>补齐反序规格选择、下单后前端库存刷新、富文本安全和测试可复跑验证</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG12" s="2" t="n"/>
-      <c r="AH12" s="2" t="n"/>
-      <c r="AI12" s="2" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>b4c75ff4b8caffc300c8ea96ba1aa8a27c67be33</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/b4c75ff4b8caffc300c8ea96ba1aa8a27c67be33</t>
+        </is>
+      </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK12" s="2" t="inlineStr"/>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T03:39:12.397Z</t>
-        </is>
-      </c>
-      <c r="AM12" s="6" t="n"/>
-      <c r="AN12" s="6" t="n"/>
-      <c r="AO12" s="6" t="n"/>
-      <c r="AP12" s="6" t="n"/>
+          <t>2026-06-19T03:52:51.180Z</t>
+        </is>
+      </c>
+      <c r="AM12" s="6" t="inlineStr">
+        <is>
+          <t>投递：实际投递内容为“单元测试销售规格价格、库存扣减、已售数量和详情富文本”，copiedSessionId 为 .480911634477292:925456f396d6805851f4d5d62024e2fa_6a34b9dda75988fec5d0e0da.6a34b9dfa75988fec5d0e0dc.6a34b9de9ad333c21ecd798a:Trae CN.T(2026/6/19 11:39:11)。等待：TRAE 状态为 completed，是否完成为是。审查/保留：工作区保留了 package.json/package-lock.json/server/server.js/src/App.vue/src/api/index.js/src/api/product.js 的修改，并新增 src/components/ProductDescription.vue、tests/、vitest.config.js；任务跟踪表 xlsx 也被修改。完成：从文件看 Trae 建立了根目录 test/test:watch 脚本、Vitest 配置、三组测试文件，并为服务端导出 app、getAppState、setAppState、formatSalesText 以支持测试。验证证据：Trae 日志尾部未读取到；Codex 只读执行 npm test 时未能进入测试阶段，失败原因是 Vite/Vitest 加载配置时尝试写入 node_modules/.vite-temp/vitest.config.js.timestamp-*.mjs，被当前只读沙箱拒绝 EPERM，因此只能确认测试文件存在和静态意图，不能确认 Trae 当时跑通过。</t>
+        </is>
+      </c>
+      <c r="AN12" s="6" t="inlineStr">
+        <is>
+          <t>完成内容：tests/useProductSpec.test.js 覆盖 unitPrice/specPriceAdjust/totalPrice/skuKey/matchedSku/currentStock/maxQuantity/quantity 边界；tests/server.test.js 覆盖 /api/order/create 扣库存、库存不足、SKU 不存在、销量接口和富文本接口；tests/description.test.js 覆盖 stripHtmlTags 与 ProductDescription 组件 v-html 渲染。配套代码新增 /api/product/:id/description、description 字段、getProductDescription、stripHtmlTags 和 ProductDescription 组件。缺口和风险：src/composables/useProductSpec.js 的 skuKey 使用 Object.values(selectedSpecs).join('-')，测试只按 color 再 version 选择，未覆盖反序选择导致 key 变成 version-color 而匹配 SKU 失败的场景；server 测试中 initialState 被保存但没有恢复，setAppState 直接改模块级 mockProduct/salesCount，测试隔离依赖每个用例手动覆盖；src/App.vue 的 fetchSkuList 仍写死 SKU 库存，handleBuyNow 下单后只有“刷新库存”空注释，所以服务端扣减库存不会反映到前端规格库存；ProductDescription.vue 第 8 行直接 v-html 渲染接口 HTML，stripHtmlTags 只是纯文本展示工具，不是 HTML 清洗，测试没有覆盖 script/onerror 等危险输入；src/App.vue 还引入了未使用的 stripHtmlTags。</t>
+        </is>
+      </c>
+      <c r="AO12" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：本轮目标是“代码测试”，但 Trae 没有留下可读取日志或测试通过输出；git diff 显示运行时代码和任务跟踪表也被修改，范围不再是单纯补单元测试；未跟踪的 tests/ 和 vitest.config.js 未出现在 diff --stat 的文件变更统计内，审查时容易漏看核心产物。产物问题：测试数量多但关键断言偏正向路径，未压住规格选择顺序、下单后前端库存刷新、富文本安全清洗、服务端状态恢复等风险；为测试导出的 getAppState/setAppState 改动了生产 server 模块形态且状态恢复设计不完整；富文本功能以 v-html 直出，新增测试反而固化了直接渲染 HTML 的行为；库存扣减和已售数量主要验证服务端 mock 状态，未覆盖 App 中购买后 UI 的库存/销量一致性。</t>
+        </is>
+      </c>
+      <c r="AP12" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git status --short、git diff --stat、rg --files、package.json、vitest.config.js、tests/useProductSpec.test.js、tests/server.test.js、tests/description.test.js、server/server.js、src/composables/useProductSpec.js、src/components/ProductSpec.vue、src/components/ProductDescription.vue、src/App.vue、src/api/product.js、src/api/index.js、src/api/order.js，并尝试执行 npm test 获取验证证据；测试执行在当前只读沙箱因 EPERM 写入 node_modules/.vite-temp 失败，未修改文件。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-115049.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2584,48 +2662,48 @@
           <t>未发送</t>
         </is>
       </c>
-      <c r="U13" s="4" t="n"/>
+      <c r="U13" s="4" t="inlineStr"/>
       <c r="V13" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
+      <c r="W13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
         </is>
       </c>
-      <c r="Z13" s="4" t="n"/>
-      <c r="AA13" s="4" t="n"/>
-      <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="4" t="n"/>
-      <c r="AE13" s="4" t="n"/>
+      <c r="Z13" s="4" t="inlineStr"/>
+      <c r="AA13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AE13" s="4" t="inlineStr"/>
       <c r="AF13" s="3" t="inlineStr">
         <is>
           <t>未提交</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="n"/>
+      <c r="AG13" s="4" t="inlineStr"/>
+      <c r="AH13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="inlineStr"/>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="AK13" s="4" t="n"/>
+      <c r="AK13" s="4" t="inlineStr"/>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
-        </is>
-      </c>
-      <c r="AM13" s="6" t="n"/>
-      <c r="AN13" s="6" t="n"/>
-      <c r="AO13" s="6" t="n"/>
-      <c r="AP13" s="6" t="n"/>
+          <t>2026-06-19T03:55:17.956Z</t>
+        </is>
+      </c>
+      <c r="AM13" s="6" t="inlineStr"/>
+      <c r="AN13" s="6" t="inlineStr"/>
+      <c r="AO13" s="6" t="inlineStr"/>
+      <c r="AP13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1050,10 +1050,14 @@
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:00:54.305Z</t>
+        </is>
+      </c>
       <c r="X3" s="4" t="inlineStr">
         <is>
           <t>.480911634477292:d808200ea68af7eb9f3630ad74289926_6a34bdc7a75988fec5d0e1ad.6a34bdc8a75988fec5d0e1af.6a34bdc89ad333c21ecd798c:Trae CN.T(2026/6/19 11:55:52)</t>
@@ -1061,38 +1065,96 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr"/>
-      <c r="AD3" s="4" t="inlineStr"/>
-      <c r="AE3" s="4" t="inlineStr"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:00:54.305Z</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>Trae CN 基本完成了核心信息区功能：在 src/components/ProductCoreInfo.vue 展示商品名称、品牌/型号、参数、销售价格和销量，并在 server/server.js 补充 mock 字段。但核心信息区未受 dataLoaded 控制，首屏异步加载前会短暂显示 ¥0.00、空标题和“已售 ”；同时没有新增组件测试、接口字段测试或构建/页面验证证据。</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>首屏加载态缺陷；测试覆盖不足；验证证据缺失；存在无关二进制变更；项目指令文件缺失</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>src/components/ProductCoreInfo.vue
+src/App.vue
+server/server.js
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+RTK.md</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>修复核心信息区加载态并补充组件/API测试</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
+          <t>已提交</t>
         </is>
       </c>
       <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>39dc65a83c1dadca54c82a3470147463152205cf</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/39dc65a83c1dadca54c82a3470147463152205cf</t>
+        </is>
+      </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK3" s="4" t="inlineStr"/>
       <c r="AL3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T03:55:54.331Z</t>
-        </is>
-      </c>
-      <c r="AM3" s="6" t="inlineStr"/>
-      <c r="AN3" s="6" t="inlineStr"/>
-      <c r="AO3" s="6" t="inlineStr"/>
-      <c r="AP3" s="6" t="inlineStr"/>
+          <t>2026-06-19T04:01:07.870Z</t>
+        </is>
+      </c>
+      <c r="AM3" s="6" t="inlineStr">
+        <is>
+          <t>投递：实际投递内容为“开发核心信息区显示商品名称、品牌型号、参数、销售价格、销量”。等待：TRAE状态为 completed，是否完成为是，但日志尾部未读取到日志，无法从日志确认中间执行步骤。审查/保留：工作区保留了 server/server.js、src/App.vue 的修改和新增 src/components/ProductCoreInfo.vue，同时还修改了二进制文件 YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx。完成：代码层面新增 ProductCoreInfo 组件并接入 App.vue，服务端商品详情接口返回 brand、model、parameters。验证证据：未看到 Trae 提供的 npm test、npm run build、页面截图或浏览器验证记录；我只读检查了 git diff、相关源码和测试文件，未执行会写入 dist 的构建命令。</t>
+        </is>
+      </c>
+      <c r="AN3" s="6" t="inlineStr">
+        <is>
+          <t>完成内容：src/components/ProductCoreInfo.vue 新增价格、原价、折扣、标题、副标题、销量评分、品牌型号、参数列表和参数展开按钮；src/App.vue 用该组件替换原内联商品信息区，并从接口数据写入 brand、model、parameters；server/server.js mockProduct 和 /api/product/:id 响应补充品牌、型号、参数字段。缺失内容：ProductCoreInfo 没有 v-if=dataLoaded 或骨架/加载态，App.vue 第 30 行会在接口返回前直接渲染，初始 displayPrice 为 0、salesText 为空，用户可能看到错误占位；tests/server.test.js 仍只断言 description、sales、订单等旧行为，没有断言 brand/model/parameters 返回；没有 ProductCoreInfo 的渲染、展开/收起或空参数状态测试。风险：新增组件是未跟踪文件，若提交/打包流程遗漏会导致 App.vue 导入失败；二进制 xlsx 修改无法审查具体内容，可能是与代码任务无关的噪声变更；RTK.md 在项目及上级扫描范围内未找到，AGENTS 指令引用无法核验。</t>
+        </is>
+      </c>
+      <c r="AO3" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae 日志尾部未读取到日志，无法确认是否执行过安装、构建、测试或页面检查；完成状态只来自任务状态和文件差异，不是来自可复现验证；还留下了 xlsx 二进制变更，审查者无法判断其必要性。产物问题：核心信息区功能虽然被实现，但缺少加载态保护，异步数据返回前会展示错误价格和空销量；新增接口字段和新增组件都没有测试覆盖；没有视觉截图或移动端页面验证，无法确认品牌型号、参数列表和底部购买栏在真实页面中是否布局正常。</t>
+        </is>
+      </c>
+      <c r="AP3" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git status、git diff -- src/App.vue src/components/ProductCoreInfo.vue server/server.js、src/components/ProductCoreInfo.vue、src/App.vue、server/server.js、package.json、server/package.json、tests/server.test.js、tests/description.test.js、tests/useProductSpec.test.js，并用 find 查找 RTK.md 未找到；因用户要求只读且构建会生成 dist，未运行 npm run build，Trae日志尾部由输入声明为未读取到日志。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-115916.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1180,17 +1242,25 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:01:11.908Z</t>
+        </is>
+      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W4" s="2" t="n"/>
-      <c r="X4" s="2" t="n"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>.480911634477292:60af1dcc14279f081e43daf5cdd8c1d8_6a34bdc7a75988fec5d0e1ad.6a34bf08a75988fec5d0e210.6a34bf089ad333c21ecd798d:Trae CN.T(2026/6/19 12:01:12)</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -1212,13 +1282,13 @@
       <c r="AI4" s="2" t="n"/>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK4" s="2" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T04:01:14.295Z</t>
         </is>
       </c>
       <c r="AM4" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1252,10 +1252,14 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:04:43.219Z</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
           <t>.480911634477292:60af1dcc14279f081e43daf5cdd8c1d8_6a34bdc7a75988fec5d0e1ad.6a34bf08a75988fec5d0e210.6a34bf089ad333c21ecd798d:Trae CN.T(2026/6/19 12:01:12)</t>
@@ -1263,38 +1267,95 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="n"/>
-      <c r="AA4" s="2" t="n"/>
-      <c r="AB4" s="2" t="n"/>
-      <c r="AC4" s="2" t="n"/>
-      <c r="AD4" s="2" t="n"/>
-      <c r="AE4" s="2" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:04:43.219Z</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>Trae CN 基本实现了服务承诺标签区：后端在 server/server.js 增加 servicePromises，前端在 src/App.vue 接入新增的 src/components/ServicePromises.vue。主要不足是新增组件仍处于未跟踪状态，任务要求中的“质保”被实现为“质保 全国联保”存在文案偏差，并且没有看到 npm test、npm run build 或页面截图验证证据。</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>功能基本完成但文案不完全一致；新增文件未纳入跟踪；缺少构建/测试/页面验证证据；任务跟踪表产生非代码改动</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>server/server.js
+src/App.vue
+src/components/ServicePromises.vue
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>补齐服务承诺标签验证：确认质保文案与需求一致，纳入新增组件，并执行测试/构建</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG4" s="2" t="n"/>
-      <c r="AH4" s="2" t="n"/>
-      <c r="AI4" s="2" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>45048c29ad7efe5c24d7b65244ccb219095ed3d2</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/45048c29ad7efe5c24d7b65244ccb219095ed3d2</t>
+        </is>
+      </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T04:01:14.295Z</t>
-        </is>
-      </c>
-      <c r="AM4" s="6" t="n"/>
-      <c r="AN4" s="6" t="n"/>
-      <c r="AO4" s="6" t="n"/>
-      <c r="AP4" s="6" t="n"/>
+          <t>2026-06-19T04:04:57.562Z</t>
+        </is>
+      </c>
+      <c r="AM4" s="6" t="inlineStr">
+        <is>
+          <t>投递内容为“开发服务承诺标签区：配送方式快递发货、质保、可交付区域全国”，TRAE 状态为 completed，是否完成标记为是。代码层面可见 Trae 在 server/server.js 的 mockProduct 和 /api/product/:id 返回值中加入 servicePromises，在 src/App.vue 初始化、赋值并渲染 ServicePromises。审查证据来自本地 git status、git diff、组件源码和测试配置；日志尾部未读取到日志，未发现 Trae 执行 npm test、npm run build、启动服务或截图验收的证据。</t>
+        </is>
+      </c>
+      <c r="AN4" s="6" t="inlineStr">
+        <is>
+          <t>产出完成了一个独立 ServicePromises 组件，按接口数组渲染配送方式、质保、可交付区域三项，并在商品核心信息后、规格选择前展示；后端接口也返回对应字段，前端 API 透传结构可以承接。缺口是没有新增组件测试或接口断言，tests/server.test.js 未覆盖 servicePromises 返回，新增组件为未跟踪文件，且“质保”被补成“全国联保”属于自行扩写，不完全等同于实际投递内容。风险主要是交付时漏掉未跟踪组件会导致 App.vue import 失败，或 UI 文案与验收口径不一致；缺少构建和页面验证使样式溢出、移动端滚动展示等问题没有证据闭环。</t>
+        </is>
+      </c>
+      <c r="AO4" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：TRAE 标记 completed，但日志尾部为空，无法确认其是否启动前后端、运行测试、执行构建或做页面人工/截图检查；git diff --stat 不包含未跟踪的 ServicePromises.vue，说明完成判定没有充分核对工作区交付完整性。产物问题：src/components/ServicePromises.vue 是核心新增文件但仍为 ?? 未跟踪；server/server.js 中质保项 value 写为“全国联保”，与投递内容只要求“质保”不完全一致；现有测试没有覆盖 /api/product/:id 返回 servicePromises，也没有前端组件渲染断言。</t>
+        </is>
+      </c>
+      <c r="AP4" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git status --short、git diff -- server/server.js src/App.vue、git diff --stat、src/components/ServicePromises.vue、src/App.vue、server/server.js、src/api/product.js、src/api/index.js、package.json、vitest.config.js、tests/server.test.js 和源码文件列表。未修改任何文件，未运行可能产生输出目录的构建命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-120332.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1590,51 +1651,59 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:05:32.894Z</t>
+        </is>
+      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="W6" s="2" t="n"/>
-      <c r="X6" s="2" t="n"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>.480911634477292:f58fa4178d2adf168ff43933aff6f9c3_6a34c00ca75988fec5d0e243.6a34c00da75988fec5d0e245.6a34c00d9ad333c21ecd798e:Trae CN.T(2026/6/19 12:05:33)</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n"/>
-      <c r="AA6" s="2" t="n"/>
-      <c r="AB6" s="2" t="n"/>
-      <c r="AC6" s="2" t="n"/>
-      <c r="AD6" s="2" t="n"/>
-      <c r="AE6" s="2" t="n"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="3" t="inlineStr">
         <is>
           <t>未提交</t>
         </is>
       </c>
-      <c r="AG6" s="2" t="n"/>
-      <c r="AH6" s="2" t="n"/>
-      <c r="AI6" s="2" t="n"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr"/>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
-        </is>
-      </c>
-      <c r="AM6" s="6" t="n"/>
-      <c r="AN6" s="6" t="n"/>
-      <c r="AO6" s="6" t="n"/>
-      <c r="AP6" s="6" t="n"/>
+          <t>2026-06-19T04:05:35.207Z</t>
+        </is>
+      </c>
+      <c r="AM6" s="6" t="inlineStr"/>
+      <c r="AN6" s="6" t="inlineStr"/>
+      <c r="AO6" s="6" t="inlineStr"/>
+      <c r="AP6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1661,49 +1661,110 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:20:21.266Z</t>
+        </is>
+      </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>.480911634477292:f58fa4178d2adf168ff43933aff6f9c3_6a34c00ca75988fec5d0e243.6a34c00da75988fec5d0e245.6a34c00d9ad333c21ecd798e:Trae CN.T(2026/6/19 12:05:33)</t>
+          <t>.480911634477292:f58fa4178d2adf168ff43933aff6f9c3_6a34c00ca75988fec5d0e243.6a34c00da75988fec5d0e245.6a34c00d9ad333c21ecd798e:Trae CN.T(2026/6/19 12:18:26)</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr"/>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:20:21.265Z</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Trae CN 已在 server/server.js 的 mock description 中加入产品参数、功能介绍、场景案例、售后保障，并在 ProductDescription.vue 增加固定分区 Tab，但实现强依赖硬编码 HTML 与外部 trae-api-cn 图片链接。tests/description.test.js 只验证 Tab 配置和点击激活态，没有验证接口富文本实际包含四个业务区块、图片可用性、滚动定位效果或页面视觉结果；本地 npm test 在只读环境因 Vitest 写入 .vite-temp 被 EPERM 阻断，未获得通过证据。</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>验证不足；富文本内容硬编码；外部图片依赖；导航与内容未绑定；测试覆盖偏表层；二进制跟踪表改动不可审查</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>server/server.js
+src/components/ProductDescription.vue
+tests/description.test.js
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>补齐详情富文本区的可验证实现：四个区块由内容配置驱动，移除不稳定外链图片，增加接口和组件断言并完成构建/测试验证</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
+          <t>已提交</t>
         </is>
       </c>
       <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>479217b676a8ea7b3f65fe5dd6d21f80be372da0</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/479217b676a8ea7b3f65fe5dd6d21f80be372da0</t>
+        </is>
+      </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK6" s="2" t="inlineStr"/>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T04:05:35.207Z</t>
-        </is>
-      </c>
-      <c r="AM6" s="6" t="inlineStr"/>
-      <c r="AN6" s="6" t="inlineStr"/>
-      <c r="AO6" s="6" t="inlineStr"/>
-      <c r="AP6" s="6" t="inlineStr"/>
+          <t>2026-06-19T04:20:34.500Z</t>
+        </is>
+      </c>
+      <c r="AM6" s="6" t="inlineStr">
+        <is>
+          <t>投递：实际投递内容为“增加详情富文本区，包含产品参数、功能介绍、场景案例和售后保障”，copiedSessionId 为 .480911634477292:f58fa4178d2adf168ff43933aff6f9c3_6a34c00ca75988fec5d0e243.6a34c00da75988fec5d0e245.6a34c00d9ad333c21ecd798e:Trae CN.T(2026/6/19 12:18:26)。等待：用户提供状态为 completed，是否完成为是，但日志尾部未读取到日志。审查/保留：当前工作区保留 4 个改动文件，server/server.js 增加富文本内容，src/components/ProductDescription.vue 增加 Tab/滚动/样式，tests/description.test.js 增加 Tab 单测，另有 xlsx 二进制变更。完成：功能表面上覆盖了短提示词要求的四类内容。验证证据：git diff --stat 显示 266 行插入、16 行删除；git diff --check 无输出；npm test 在只读环境失败，原因是 Vitest 需要写入 node_modules/.vite-temp，未形成测试通过证据；未发现 Trae 提供的构建、截图或浏览器验证日志。</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="inlineStr">
+        <is>
+          <t>产出完成了 mock 商品详情富文本扩展，包含参数表、功能段落、4 个场景案例卡片和售后列表；组件侧增加了固定的四个分区 Tab、scrollIntoView 和 IntersectionObserver 激活态。缺口是 Tab 配置写死，未从实际富文本结构派生，initialHtml 不含目标 h2 时仍显示并可激活不存在的分区；场景案例图片直接引用 trae-api-cn text_to_image 外链，离线、限流或接口变更会导致详情区破图；测试没有断言 server 返回的四个区块标题和 section id，也没有验证真实 HTML 渲染出的场景卡片、售后列表、滚动定位与移动端表现。风险是详情页看似完成但可用性依赖 mock 字符串和外部服务，后续换商品或真实 CMS 内容时导航和样式容易失配。</t>
+        </is>
+      </c>
+      <c r="AO6" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae 状态为 completed 但没有可读取日志，无法确认是否运行过测试、构建或浏览器预览；还改动了 YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx 这类二进制文件，无法从 diff 审查具体内容。产物问题：server/server.js 把整段详情内容硬编码进 mock description，没有抽成可维护结构；ProductDescription.vue 的 detailSections 与实际 HTML 内容没有同步机制，缺失目标元素时测试反而接受只切换 activeSection；tests/description.test.js 新增用例主要覆盖组件内部配置，没有覆盖本轮最关键的业务验收点，即产品参数、功能介绍、场景案例、售后保障是否从接口到页面完整呈现。</t>
+        </is>
+      </c>
+      <c r="AP6" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git status、git diff --stat、server/server.js、src/components/ProductDescription.vue、tests/description.test.js、tests/server.test.js、src/api/product.js、package.json，并用 rg 搜索了产品参数/功能介绍/场景案例/售后保障/section-params 的出现位置。尝试运行 npm test，因当前只读沙箱禁止 Vitest 写入 node_modules/.vite-temp 而失败；find .. -name AGENTS.md -o -name RTK.md 未找到本地 AGENTS.md 或 RTK.md 文件。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-121829.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1791,17 +1852,25 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:20:53.527Z</t>
+        </is>
+      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>.480911634477292:ec1059e5a95a52c3b568bf42cf056cf5_6a34c00ca75988fec5d0e243.6a34c3a6a75988fec5d0e2d5.6a34c3a69ad333c21ecd798f:Trae CN.T(2026/6/19 12:20:54)</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -1823,13 +1892,13 @@
       <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK7" s="4" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK7" s="4" t="inlineStr"/>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T04:20:55.940Z</t>
         </is>
       </c>
       <c r="AM7" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -1862,10 +1862,14 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:24:03.333Z</t>
+        </is>
+      </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
           <t>.480911634477292:ec1059e5a95a52c3b568bf42cf056cf5_6a34c00ca75988fec5d0e243.6a34c3a6a75988fec5d0e2d5.6a34c3a69ad333c21ecd798f:Trae CN.T(2026/6/19 12:20:54)</t>
@@ -1873,38 +1877,95 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="n"/>
-      <c r="AE7" s="4" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:24:03.332Z</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>当前代码中已有底部固定下单栏，`src/App.vue` 包含收藏、客服、购物车入口以及“加入购物车”“立即购买”按钮，但本轮 `功能迭代-3` 没有产生新的代码提交或源码 diff，只留下任务跟踪表二进制变更。下单栏实际最早已存在于 `2572503`，`744bc4a` 只补过加入购物车/立即购买点击逻辑；本轮缺少构建、测试、浏览器截图或移动端布局验证证据。</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>本轮无源码产出；复用既有实现冒充本轮完成；验证证据缺失；移动端布局风险；交互闭环不足；二进制变更不可审查</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>src/App.vue
+src/composables/useProductSpec.js
+tests/useProductSpec.test.js
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>补齐底部固定下单栏的本轮可交付：确认按钮顺序为客服、收藏、加入购物车、立即购买，移除多余购物车入口或说明保留原因，补充移动端适配、收藏/客服交互状态、下单后库存刷新，并运行构建和页面验证</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr">
+        <is>
+          <t>d88d933f6259dc8275aa7d2c0898872ab5111319</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/d88d933f6259dc8275aa7d2c0898872ab5111319</t>
+        </is>
+      </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK7" s="4" t="inlineStr"/>
       <c r="AL7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T04:20:55.940Z</t>
-        </is>
-      </c>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
+          <t>2026-06-19T04:24:16.099Z</t>
+        </is>
+      </c>
+      <c r="AM7" s="6" t="inlineStr">
+        <is>
+          <t>投递：本轮实际投递内容为“增加底部固定下单栏：客服、收藏、加入购物车、立即购买”，copiedSessionId 指向 Trae CN 2026/6/19 12:20:54。等待：`.trae-worker-logs/worker-9324-20260619-main/latest.log` 显示 row7 功能迭代-3 于 12:21:11 后开始 heartbeat，并在 12:21:51 启动 Codex CLI 只读分析，输出目标为 `.trae-codex-analysis/analysis-20260619-122204.json`。审查/保留：本地没有生成该 `analysis-20260619-122204.json` 文件；`git status --short` 只显示 `YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx` 被修改，`git diff -- src/App.vue` 为空，`git ls-files --others --exclude-standard` 为空。完成：用户提供 TRAE 状态为 completed、是否完成为是，但 `git log` 最新提交仍是上一轮 `479217b` 功能迭代-2，没有本轮功能迭代-3 的提交。验证证据：只读检查确认 `src/App.vue` 已有固定底栏代码，但该代码在 `HEAD` 中已存在；未看到 Trae 本轮执行 `npm test`、`npm run build`、启动前后端或浏览器截图验证的证据。</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="inlineStr">
+        <is>
+          <t>代码现状：`src/App.vue` 第 63-94 行有 `footer.buy-bar`，第 323-418 行用 `position: fixed; bottom: 0` 实现底部固定栏，包含“收藏”“客服”“购物车”三个图标按钮、合计价格、“加入购物车”和“立即购买”。`handleAddToCart` 第 230-235 行只 `console.log` 并 `alert('已加入购物车')`，没有真实购物车状态；`handleBuyNow` 第 207-227 行调用 `createOrder`，但下单成功后第 219-221 行库存刷新仍是空注释。和本轮需求相比，栏位不是严格的“客服、收藏、加入购物车、立即购买”四项，而是多了一个“购物车”入口且顺序为收藏、客服、购物车、加入购物车、立即购买；收藏和客服按钮没有点击处理。样式没有响应式断点，左侧 3 个 56px 图标、合计区和两个 24px padding 的按钮在窄屏上有挤压风险。测试方面，现有 `tests/useProductSpec.test.js` 覆盖了规格/价格/库存，但没有覆盖底部栏渲染、按钮顺序、点击购物车、立即购买禁用态或移动端布局。</t>
+        </is>
+      </c>
+      <c r="AO7" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae CN 标记本轮 completed，但本地证据显示本轮没有源码 diff、没有新提交、没有生成对应只读分析 JSON；只有任务跟踪表 xlsx 二进制变化，无法审查具体记录内容。日志只看到 row7 启动、heartbeat 和分析启动，没有 row7 完成摘要、commitId、构建/测试/截图输出。产物问题：底部下单栏不是本轮新增代码，而是早在 `2572503` 就已有基础 UI，`744bc4a` 才补过购买相关点击；当前实现与短提示词四项要求不完全一致，多出“购物车”图标入口且客服/收藏无交互；加入购物车是假成功提示，没有持久状态；立即购买后不刷新规格库存；缺少窄屏适配和自动化/人工验证，不能证明固定栏在真实页面底部不遮挡、不溢出且购买链路可用。</t>
+        </is>
+      </c>
+      <c r="AP7" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 `pwd`、`rg --files`、`git status --short`、`git diff --stat`、`git diff -- src/App.vue`、`git log --oneline --stat -5`、`git reflog --date=iso -8`、`.trae-worker-logs/worker-9324-20260619-main/latest.log`、`.trae-codex-analysis` 文件列表、`src/App.vue`、`src/composables/useProductSpec.js`、`tests/useProductSpec.test.js`、`server/server.js`、`package.json`、`server/package.json`；并用 `git show &lt;rev&gt;:src/App.vue` 追溯 `buy-bar/加入购物车/立即购买/客服/收藏/购物车` 最早出现的提交。未修改任何文件，未运行会写入项目目录的构建或测试命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-122204.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2199,51 +2260,59 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:24:54.617Z</t>
+        </is>
+      </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>.480911634477292:07a8b0ea59f2753725ec739429d85433_6a34c495a75988fec5d0e2e1.6a34c497a75988fec5d0e2e3.6a34c4979ad333c21ecd7990:Trae CN.T(2026/6/19 12:24:55)</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
         </is>
       </c>
-      <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n"/>
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="inlineStr"/>
+      <c r="AE9" s="4" t="inlineStr"/>
       <c r="AF9" s="3" t="inlineStr">
         <is>
           <t>未提交</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="n"/>
-      <c r="AI9" s="4" t="n"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK9" s="4" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK9" s="4" t="inlineStr"/>
       <c r="AL9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
-        </is>
-      </c>
-      <c r="AM9" s="6" t="n"/>
-      <c r="AN9" s="6" t="n"/>
-      <c r="AO9" s="6" t="n"/>
-      <c r="AP9" s="6" t="n"/>
+          <t>2026-06-19T04:24:57.034Z</t>
+        </is>
+      </c>
+      <c r="AM9" s="6" t="inlineStr"/>
+      <c r="AN9" s="6" t="inlineStr"/>
+      <c r="AO9" s="6" t="inlineStr"/>
+      <c r="AP9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -2270,10 +2270,14 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:32:02.602Z</t>
+        </is>
+      </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
           <t>.480911634477292:07a8b0ea59f2753725ec739429d85433_6a34c495a75988fec5d0e2e1.6a34c497a75988fec5d0e2e3.6a34c4979ad333c21ecd7990:Trae CN.T(2026/6/19 12:24:55)</t>
@@ -2281,38 +2285,97 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="inlineStr"/>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:32:02.601Z</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>Trae CN 在 server/server.js 新增了 /api/order/pay，并把库存扣减、已售累加从下单阶段迁到支付阶段，tests/server.test.js 也补了支付后扣库存和销量累加用例。主要不足是缺少可采信的执行日志和测试通过证据，当前只读环境运行 npm test 被 Vite 写入 node_modules/.vite-temp 的 EPERM 阻断；前端 src/App.vue 将“立即购买”直接串联下单和支付，未形成真实付款步骤验证，且“已售加1”语义未澄清为按订单加 1 还是按购买数量累加。</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>验证证据不足；支付流程语义简化；前端闭环验证缺失；需求语义未澄清；无关二进制文件改动</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>server/server.js
+src/App.vue
+src/api/index.js
+src/api/order.js
+tests/server.test.js
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>补充真实支付完成后的库存和已售更新验证，澄清已售是每单+1还是按数量累加，并去除无关文件改动</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
+          <t>已提交</t>
         </is>
       </c>
       <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr">
+        <is>
+          <t>269648e6ae4266cd341926c9dce66c45c1943095</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/269648e6ae4266cd341926c9dce66c45c1943095</t>
+        </is>
+      </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK9" s="4" t="inlineStr"/>
       <c r="AL9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T04:24:57.034Z</t>
-        </is>
-      </c>
-      <c r="AM9" s="6" t="inlineStr"/>
-      <c r="AN9" s="6" t="inlineStr"/>
-      <c r="AO9" s="6" t="inlineStr"/>
-      <c r="AP9" s="6" t="inlineStr"/>
+          <t>2026-06-19T04:32:16.156Z</t>
+        </is>
+      </c>
+      <c r="AM9" s="6" t="inlineStr">
+        <is>
+          <t>实际投递内容为“修复库存付款后没有减少，已售数量没有付款后加1”，copiedSessionId 对应 Trae CN，TRAE 状态为 completed。日志尾部未读取到，因此无法确认 Trae 是否执行过测试或人工验收；本地仅能看到完成后保留了 6 个变更文件。代码审查显示 Trae 的处理路径是：后端新增订单内存 Map，/api/order/create 只创建 pending 订单不扣库存，/api/order/pay 才扣减 SKU 库存并累加 salesCount；前端 handleBuyNow 创建订单后立即调用 payOrder，再刷新销量和当前 SKU 库存；测试侧重写并新增了 server.test.js 用例。验证证据方面，git diff --check 无输出；npm test 在只读沙箱中因 Vite 尝试写 node_modules/.vite-temp/vitest.config.js.timestamp*.mjs 失败，无法证明测试通过。</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="inlineStr">
+        <is>
+          <t>产物基本覆盖了后端核心修复点：付款接口成功时 sku.stock -= order.quantity，salesCount += order.quantity，重复支付会返回“订单已支付”，支付时库存不足不会扣减，创建订单阶段不再提前扣库存或销量。前端也接入了 payOrder，并在支付成功后刷新 salesInfo 和当前 SKU 的 stock。缺口是付款流程被简化成点击“立即购买”后自动支付，没有独立支付页、支付回调或支付状态确认；UI 验证缺失，测试只覆盖接口，没有覆盖 App.vue 点击后销量和库存展示是否正确更新；如果业务期望“已售数量每笔付款 +1”，当前实现和测试实际是按购买数量累加。另一个风险是订单和库存仍是进程内 mock 状态，服务重启丢失，且修改了任务跟踪表 xlsx 这个与代码修复无直接关系的二进制文件。</t>
+        </is>
+      </c>
+      <c r="AO9" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：未读取到 Trae 日志，无法确认其是否有等待、审查、测试运行和验收记录；本地没有测试通过输出，Codex 只读复验也被 EPERM 阻断，只能确认 diff 形态而不能确认完整测试绿灯；还留下了 xlsx 二进制改动，增加审查噪音。产物问题：后端修复方向正确但偏 mock，实现依赖内存 Map，不是真实订单/支付链路；前端把付款自动化为下单后立即支付，不能证明“付款后”这一状态转换在真实流程中成立；测试未覆盖前端展示更新和真实用户操作闭环；“已售加1”与 salesCount += quantity 的口径未被明确说明，可能与需求字面不一致。</t>
+        </is>
+      </c>
+      <c r="AP9" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 git diff -- server/server.js、src/App.vue、src/api/index.js、src/api/order.js、tests/server.test.js，读取了 src/api/product.js、src/api/request.js、src/composables/useProductSpec.js、src/components/ProductSpec.vue、package.json、server/package.json、vitest.config.js，并用 rg 搜索 order/pay、payOrder、getSkuStock、salesCount、stock 等调用点；执行 git diff --name-only 和 git diff --check；尝试 npm test，因只读环境禁止 Vite 写入 node_modules/.vite-temp 而无法完成测试运行。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-123013.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2400,17 +2463,25 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:32:34.719Z</t>
+        </is>
+      </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W10" s="2" t="n"/>
-      <c r="X10" s="2" t="n"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>.480911634477292:659525a91290632411d40ca9d6d519c3_6a34c495a75988fec5d0e2e1.6a34c663a75988fec5d0e34d.6a34c6639ad333c21ecd7991:Trae CN.T(2026/6/19 12:32:35)</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -2432,13 +2503,13 @@
       <c r="AI10" s="2" t="n"/>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK10" s="2" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr"/>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T04:32:37.191Z</t>
         </is>
       </c>
       <c r="AM10" s="6" t="n"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -2473,10 +2473,14 @@
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="n"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:41:52.168Z</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
           <t>.480911634477292:659525a91290632411d40ca9d6d519c3_6a34c495a75988fec5d0e2e1.6a34c663a75988fec5d0e34d.6a34c6639ad333c21ecd7991:Trae CN.T(2026/6/19 12:32:35)</t>
@@ -2484,38 +2488,94 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n"/>
-      <c r="AA10" s="2" t="n"/>
-      <c r="AB10" s="2" t="n"/>
-      <c r="AC10" s="2" t="n"/>
-      <c r="AD10" s="2" t="n"/>
-      <c r="AE10" s="2" t="n"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:41:52.168Z</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>Trae CN 将 `src/App.vue` 的立即购买改成弹出新增 `src/components/OrderConfirm.vue` 确认弹窗，但没有统一确认页展示价格与后端 `createOrder` 实际计价来源，仍依赖前端硬编码 `mockSkuList`。本轮没有新增覆盖“选择规格 -&gt; 立即购买 -&gt; 确认页价格/规格 -&gt; 下单价格”的测试，也未看到构建、测试或页面验证证据；同时还改动了任务跟踪表二进制文件，产物范围不够聚焦。</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>修复偏离需求；前后端价格源未统一；缺少端到端链路验证；缺少新增测试；无验证证据；非代码文件被改动</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>src/App.vue
+src/components/OrderConfirm.vue
+YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>统一立即购买确认页与下单接口的规格价格来源并补充测试</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
-        </is>
-      </c>
-      <c r="AG10" s="2" t="n"/>
-      <c r="AH10" s="2" t="n"/>
-      <c r="AI10" s="2" t="n"/>
+          <t>已提交</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>13c80c500870173625444442688693b40417d1f1</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/13c80c500870173625444442688693b40417d1f1</t>
+        </is>
+      </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK10" s="2" t="inlineStr"/>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T04:32:37.191Z</t>
-        </is>
-      </c>
-      <c r="AM10" s="6" t="n"/>
-      <c r="AN10" s="6" t="n"/>
-      <c r="AO10" s="6" t="n"/>
-      <c r="AP10" s="6" t="n"/>
+          <t>2026-06-19T04:42:05.384Z</t>
+        </is>
+      </c>
+      <c r="AM10" s="6" t="inlineStr">
+        <is>
+          <t>投递：本轮实际投递内容为“修复立即购买进入下单确认页时规格价格不一致”，copiedSessionId 为 .480911634477292:659525a91290632411d40ca9d6d519c3_6a34c495a75988fec5d0e2e1.6a34c663a75988fec5d0e34d.6a34c6639ad333c21ecd7991:Trae CN.T(2026/6/19 12:32:35)。等待：TRAE 状态为 completed，是否完成为是。审查/保留：工作区保留了 `src/App.vue` 修改、未跟踪的 `src/components/OrderConfirm.vue`，以及 `YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx` 二进制修改；`git diff --stat` 只显示 `App.vue` 37 行新增/7 行删除和 xlsx 变化，未跟踪组件不在 diff stat 内。完成：Trae 主要完成了确认弹窗接入和支付确认动作迁移。验证证据：未读取到 Trae 日志；只读审查中未发现 Trae 留下的测试、构建、截图或手动验证记录，本次 Codex 也未运行会产生构建产物的命令。</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="inlineStr">
+        <is>
+          <t>产出完成部分：`src/App.vue` 引入 `OrderConfirm`，点击立即购买时先检查 `currentSkuKey`，再显示确认弹窗；`handleConfirmPay` 中继续调用 `createOrder` 和 `payOrder`；新增组件展示商品图、标题、规格、单价、数量和合计。缺失部分：没有真正建立“下单确认页”或路由，只是弹窗；确认弹窗展示价格仍来自 `currentUnitPrice`，该值由前端 `fetchSkuList` 内硬编码 SKU 价格调整计算，后端订单价格则由 `server/server.js` 的 `mockProduct.skuList` 计算，两套数据源仍可能不一致；确认前没有以 `createOrder` 返回的 `unitPrice/totalPrice` 校准展示，也没有请求服务端实时 SKU 价格。风险：如果后端 SKU 调价、库存接口返回不同 `priceAdjust`、或前端硬编码 SKU 表与服务端不一致，确认页仍可能显示错误价格；新增 `ordering` 状态已经不再被设置但按钮仍绑定 `:disabled="ordering"`，状态语义残留；没有新增 App/组件测试覆盖本次回归场景。</t>
+        </is>
+      </c>
+      <c r="AO10" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae 状态虽为 completed，但没有可读日志、测试输出、构建输出或页面操作证据，无法证明修复过目标 bug；还改动了 xlsx 任务跟踪表，和本轮功能修复无直接关系。产物问题：修复思路停留在新增确认弹窗，未解决价格不一致的根因，即前端确认价和后端订单价仍来自不同数据源；`OrderConfirm.vue` 未被测试覆盖，`tests/useProductSpec.test.js` 和 `tests/server.test.js` 只覆盖规格计算/后端订单，未覆盖立即购买进入确认页后的规格与价格一致性；如果需求明确是“下单确认页”，当前弹窗实现也与页面级确认流程不一致。</t>
+        </is>
+      </c>
+      <c r="AP10" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 `git status --short`、`git diff --stat`、`git diff -- src/App.vue`、`src/App.vue`、`src/components/OrderConfirm.vue`、`src/components/ProductSpec.vue`、`src/composables/useProductSpec.js`、`src/api/order.js`、`src/api/request.js`、`server/server.js`、`tests/useProductSpec.test.js`、`tests/server.test.js`，并用 `rg` 搜索了规格、价格、下单和确认页相关引用。未修改任何文件，未运行会写入产物的构建命令；因 Trae 日志尾部显示未读取到日志，过程判断主要基于用户提供状态和本地工作区证据。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-124015.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3007,17 +3067,25 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:42:15.809Z</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>.480911634477292:230b5d2fb2e48d288a8caee3a4e7012f_6a34c8a7a75988fec5d0e38c.6a34c8a8a75988fec5d0e38e.6a34c8a89ad333c21ecd7992:Trae CN.T(2026/6/19 12:42:16)</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -3039,13 +3107,13 @@
       <c r="AI13" s="4" t="inlineStr"/>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>已投递</t>
         </is>
       </c>
       <c r="AK13" s="4" t="inlineStr"/>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T03:55:17.956Z</t>
+          <t>2026-06-19T04:42:18.261Z</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr"/>

--- a/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+++ b/YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
@@ -3077,10 +3077,14 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:46:51.195Z</t>
+        </is>
+      </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
           <t>.480911634477292:230b5d2fb2e48d288a8caee3a4e7012f_6a34c8a7a75988fec5d0e38c.6a34c8a8a75988fec5d0e38e.6a34c8a89ad333c21ecd7992:Trae CN.T(2026/6/19 12:42:16)</t>
@@ -3088,38 +3092,103 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>未分析</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr"/>
-      <c r="AD13" s="4" t="inlineStr"/>
-      <c r="AE13" s="4" t="inlineStr"/>
+          <t>已分析</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:46:51.194Z</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
+          <t>本轮“代码解读-1”没有在仓库中生成二开手册、README/Markdown 说明或可检索的解读产物，当前只看到 `YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx` 二进制变更。源码里规格、库存、富文本和购买链路分别落在 `ProductSpec/useProductSpec`、`server/server.js`、`ProductDescription.vue`、`App.vue/OrderConfirm.vue/order API`，但 Trae 没有留下针对这些文件的结构化说明、风险标注或验证证据。</t>
+        </is>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>解读产物缺失；只改二进制跟踪表；缺少源码级引用；缺少验证证据；二开风险未说明；本地交付不可复核</t>
+        </is>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx
+src/App.vue
+src/components/ProductSpec.vue
+src/composables/useProductSpec.js
+src/components/ProductDescription.vue
+src/components/OrderConfirm.vue
+src/api/product.js
+src/api/order.js
+server/server.js
+tests/useProductSpec.test.js
+tests/server.test.js
+tests/description.test.js</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>输出销售商品详情二开手册到 Markdown：按文件说明规格、库存、富文本和购买链路，并标注风险与验证命令</t>
+        </is>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>02-add-files-commit.sh</t>
+        </is>
+      </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>未提交</t>
+          <t>已提交</t>
         </is>
       </c>
       <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
+          <t>581ec74d6d45132323e750005b43271bff8cbd1b</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/zhijie435/trae-yxz-004-c-sale-product-detail/commit/581ec74d6d45132323e750005b43271bff8cbd1b</t>
+        </is>
+      </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>已投递</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="AK13" s="4" t="inlineStr"/>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19T04:42:18.261Z</t>
-        </is>
-      </c>
-      <c r="AM13" s="6" t="inlineStr"/>
-      <c r="AN13" s="6" t="inlineStr"/>
-      <c r="AO13" s="6" t="inlineStr"/>
-      <c r="AP13" s="6" t="inlineStr"/>
+          <t>2026-06-19T04:47:04.601Z</t>
+        </is>
+      </c>
+      <c r="AM13" s="6" t="inlineStr">
+        <is>
+          <t>投递：实际投递内容为“解读销售商品详情的二开手册，说明规格、库存、富文本和购买链路”，copiedSessionId 指向 Trae CN 2026/6/19 12:42:16 的代码解读任务。等待：用户提供 TRAE 状态为 completed、是否完成为是；本地 worker 日志显示 row13 代码解读-1 于 12:42:33 启动，12:44:53 触发 Codex 只读分析，尾部只到 12:45:53 heartbeat，未看到 row13 完成摘要、commitId 或验证输出。审查/保留：`git status --short` 仅显示 `YXZ-CN-004-C端销售商品详情-任务跟踪表.xlsx` 被修改，`git diff --stat` 也只有该 xlsx 二进制大小变化；`git log` 最新提交仍是上一轮 Bug 修复-3，不是本轮代码解读。完成：本地未发现新增或修改的二开手册文件，`rg` 搜索二开、手册、代码解读、规格、库存、富文本、购买链路未命中新增文档内容。验证证据：未发现 Trae 留下的构建、测试、页面截图或手册审查记录；`.trae-codex-analysis` 中最新文件仍是 12:40 的上一轮分析，未生成日志里提到的 `analysis-20260619-124455.json`。</t>
+        </is>
+      </c>
+      <c r="AN13" s="6" t="inlineStr">
+        <is>
+          <t>Trae 本轮可确认完成的本地产物只有任务跟踪表状态类二进制写入，不能作为可审查的二开手册。项目实际具备可解读对象：规格选择在 `src/components/ProductSpec.vue` 和 `src/composables/useProductSpec.js`，库存查询/扣减在 `server/server.js`、`src/api/product.js` 和 `src/App.vue` 的 `refreshStock`，富文本在 `server/server.js` 的 `description`、`src/components/ProductDescription.vue` 的 `v-html` 与分区 Tab，购买链路在 `src/App.vue` 的 `handleBuyNow/handleConfirmPay`、`src/components/OrderConfirm.vue`、`src/api/order.js` 和 `/api/order/create`、`/api/order/pay`。缺失是没有把上述链路整理成二开手册，没有说明接口字段、组件事件、状态流转、扩展点和测试覆盖，也没有标出已有风险：前端仍有硬编码 `mockSkuList` 与后端 SKU 数据双源，`v-html` 缺少 HTML 清洗边界，0 库存数量逻辑仍存在 `maxQuantity` 至少为 1 的语义风险，购买链路是确认弹窗后立即创建并支付的 mock 流程。</t>
+        </is>
+      </c>
+      <c r="AO13" s="6" t="inlineStr">
+        <is>
+          <t>过程问题：Trae 标记 completed，但本地没有本轮提交、没有可读解读文件、没有对应 Codex 分析 JSON、没有测试或构建输出；唯一变更是 xlsx 二进制文件，无法通过 diff 审查其具体内容是否满足“二开手册”。产物问题：短提示词要求说明规格、库存、富文本和购买链路，但仓库中没有 README、Markdown、txt 或其他文档承载这些说明；也没有按源码文件给出二开入口、数据结构、接口契约、事件流和验证命令，接手者仍需要自行阅读 `App.vue`、`ProductSpec.vue`、`useProductSpec.js`、`ProductDescription.vue`、`server/server.js` 和测试文件才能理解链路。</t>
+        </is>
+      </c>
+      <c r="AP13" s="6" t="inlineStr">
+        <is>
+          <t>Codex CLI：Codex CLI 只读分析；实际查看了 `git status --short`、`git diff --stat`、`git diff --name-status`、`git log --oneline --stat`、worker 日志 `.trae-worker-logs/worker-9324-20260619-main/worker-20260619-115528.log`、`.trae-codex-analysis/*.json`、xlsx 内部 XML 文本抽取结果，以及 `src/App.vue`、`src/components/ProductSpec.vue`、`src/composables/useProductSpec.js`、`src/components/ProductDescription.vue`、`src/components/OrderConfirm.vue`、`src/api/product.js`、`src/api/order.js`、`server/server.js`、`tests/useProductSpec.test.js`、`tests/server.test.js`。同时用 `find` 和 `rg` 搜索 Markdown/手册/二开/代码解读相关文件与文本；未修改任何文件，未运行会写入产物的构建或测试命令。
+Codex CLI输出：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/yxz-trae-projects/004-C端销售商品详情/.trae-codex-analysis/analysis-20260619-124455.json
+参考：https://docs.qq.com/smartsheet/DS2RueURWTUJYakp0?tab=sc_xXoEj8&amp;_t=1780819132566&amp;nlc=1&amp;viewId=vO3YC0
+已读取腾讯文档导出的“不满意原因填写指引”页；该页要求过程与产物分别分析，定位具体步骤/文件/证据，禁止只写笼统评价，也不能把环境/网络波动当作模型问题。
+本地证据：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide-export.xlsx
+结构化摘录：/Users/wuzhijie/Documents/xiaohongshu/biaozhu/trae-web-projects/TRAE-CN-dissatisfaction-guide.json
+本地分析维度：需求闭环、技术栈一致性、可运行性、测试验证、异常处理、工程化配置、占位实现、Git归档状态。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3203,17 +3272,25 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>未发送</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="n"/>
+          <t>已发送</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19T04:47:16.251Z</t>
+        </is>
+      </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
       <c r="W14" s="2" t="n"/>
-      <c r="X14" s="2" t="n"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>.480911634477292:46f9829e74f3cad8f87977da6fe2ab68_6a34c9d3a75988fec5d0e3ca.6a34c9d5a75988fec5d0e3cc.6a34c9d59ad333c21ecd7993:Trae CN.T(2026/6/19 12:47:17)</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>未分析</t>
@@ -3235,13 +3312,13 @@
       <c r="AI14" s="2" t="n"/>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="AK14" s="2" t="n"/>
+          <t>已投递</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr"/>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-19T10:32:29</t>
+          <t>2026-06-19T04:47:18.730Z</t>
         </is>
       </c>
       <c r="AM14" s="6" t="n"/>
